--- a/Datas/HomeEquipmentData.xlsx
+++ b/Datas/HomeEquipmentData.xlsx
@@ -18,8 +18,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>作者</author>
+  </authors>
+  <commentList>
+    <comment ref="D3" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve"> 生产设施,生活设施</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -107,13 +141,20 @@
   <si>
     <t>双人床</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>homeEquipType</t>
+  </si>
+  <si>
+    <t>1328,547,405</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,6 +175,19 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -156,13 +210,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -443,17 +500,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:D19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:E19"/>
   <sheetFormatPr defaultColWidth="9.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.75" style="1"/>
-    <col min="2" max="3" width="16.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="48.125" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.75" style="1"/>
+    <col min="2" max="4" width="16.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="48.125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -464,10 +521,13 @@
         <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -478,10 +538,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2100</v>
       </c>
@@ -491,8 +554,14 @@
       <c r="C4" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2101</v>
       </c>
@@ -502,8 +571,14 @@
       <c r="C5" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>2102</v>
       </c>
@@ -513,8 +588,14 @@
       <c r="C6" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>2103</v>
       </c>
@@ -524,8 +605,14 @@
       <c r="C7" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2104</v>
       </c>
@@ -535,8 +622,14 @@
       <c r="C8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>2105</v>
       </c>
@@ -546,8 +639,14 @@
       <c r="C9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>2106</v>
       </c>
@@ -557,8 +656,14 @@
       <c r="C10" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>2107</v>
       </c>
@@ -568,8 +673,14 @@
       <c r="C11" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>2108</v>
       </c>
@@ -579,8 +690,14 @@
       <c r="C12" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>2109</v>
       </c>
@@ -590,8 +707,14 @@
       <c r="C13" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>2110</v>
       </c>
@@ -601,8 +724,14 @@
       <c r="C14" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>2111</v>
       </c>
@@ -612,8 +741,14 @@
       <c r="C15" s="1">
         <v>1017</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>2112</v>
       </c>
@@ -623,8 +758,14 @@
       <c r="C16" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>2113</v>
       </c>
@@ -634,8 +775,14 @@
       <c r="C17" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>2200</v>
       </c>
@@ -645,8 +792,14 @@
       <c r="C18" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>2201</v>
       </c>
@@ -655,11 +808,18 @@
       </c>
       <c r="C19" s="1">
         <v>0</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3">
+        <v>405</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Datas/HomeEquipmentData.xlsx
+++ b/Datas/HomeEquipmentData.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -148,6 +148,9 @@
   <si>
     <t>1328,547,405</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>manufatureId</t>
   </si>
 </sst>
 </file>
@@ -501,16 +504,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:E19"/>
+  <dimension ref="A2:F19"/>
   <sheetFormatPr defaultColWidth="9.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.75" style="1"/>
     <col min="2" max="4" width="16.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="48.125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.75" style="1"/>
+    <col min="5" max="5" width="15" style="1" customWidth="1"/>
+    <col min="6" max="6" width="48.125" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -524,10 +528,13 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -541,10 +548,13 @@
         <v>23</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2100</v>
       </c>
@@ -557,11 +567,14 @@
       <c r="D4" s="1">
         <v>0</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
         <v>1328</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2101</v>
       </c>
@@ -574,11 +587,14 @@
       <c r="D5" s="1">
         <v>0</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
         <v>1328</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>2102</v>
       </c>
@@ -591,11 +607,14 @@
       <c r="D6" s="1">
         <v>0</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
         <v>1328</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>2103</v>
       </c>
@@ -608,11 +627,14 @@
       <c r="D7" s="1">
         <v>0</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
         <v>1328</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2104</v>
       </c>
@@ -620,16 +642,19 @@
         <v>11</v>
       </c>
       <c r="C8" s="1">
-        <v>0</v>
+        <v>1091</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="1">
+        <v>5001</v>
+      </c>
+      <c r="F8" s="3">
         <v>1328</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>2105</v>
       </c>
@@ -642,11 +667,14 @@
       <c r="D9" s="1">
         <v>0</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
         <v>1328</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>2106</v>
       </c>
@@ -659,11 +687,14 @@
       <c r="D10" s="1">
         <v>0</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
         <v>1328</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>2107</v>
       </c>
@@ -676,11 +707,14 @@
       <c r="D11" s="1">
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>2108</v>
       </c>
@@ -693,11 +727,14 @@
       <c r="D12" s="1">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>2109</v>
       </c>
@@ -710,11 +747,14 @@
       <c r="D13" s="1">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>2110</v>
       </c>
@@ -727,11 +767,14 @@
       <c r="D14" s="1">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>2111</v>
       </c>
@@ -744,11 +787,14 @@
       <c r="D15" s="1">
         <v>0</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
         <v>547</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>2112</v>
       </c>
@@ -761,11 +807,14 @@
       <c r="D16" s="1">
         <v>0</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
         <v>547</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>2113</v>
       </c>
@@ -778,11 +827,14 @@
       <c r="D17" s="1">
         <v>0</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
         <v>547</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>2200</v>
       </c>
@@ -795,11 +847,14 @@
       <c r="D18" s="1">
         <v>1</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
         <v>405</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>2201</v>
       </c>
@@ -812,7 +867,10 @@
       <c r="D19" s="1">
         <v>1</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="1">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3">
         <v>405</v>
       </c>
     </row>

--- a/Datas/HomeEquipmentData.xlsx
+++ b/Datas/HomeEquipmentData.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -92,10 +92,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>炖煮锅</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>冷餐台</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -151,6 +147,13 @@
   </si>
   <si>
     <t>manufatureId</t>
+  </si>
+  <si>
+    <t>搅拌器</t>
+  </si>
+  <si>
+    <t>蒸煮锅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -504,7 +507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:F19"/>
+  <dimension ref="A2:F20"/>
   <sheetFormatPr defaultColWidth="9.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.75" style="1"/>
@@ -545,10 +548,10 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>3</v>
@@ -562,13 +565,13 @@
         <v>7</v>
       </c>
       <c r="C4" s="1">
-        <v>0</v>
+        <v>1201</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
       </c>
-      <c r="E4" s="1">
-        <v>0</v>
+      <c r="E4">
+        <v>5007</v>
       </c>
       <c r="F4" s="3">
         <v>1328</v>
@@ -582,13 +585,13 @@
         <v>8</v>
       </c>
       <c r="C5" s="1">
-        <v>0</v>
+        <v>1202</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
       </c>
-      <c r="E5" s="1">
-        <v>0</v>
+      <c r="E5">
+        <v>5008</v>
       </c>
       <c r="F5" s="3">
         <v>1328</v>
@@ -602,13 +605,13 @@
         <v>9</v>
       </c>
       <c r="C6" s="1">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
-      <c r="E6" s="1">
-        <v>0</v>
+      <c r="E6">
+        <v>5003</v>
       </c>
       <c r="F6" s="3">
         <v>1328</v>
@@ -618,17 +621,17 @@
       <c r="A7" s="2">
         <v>2103</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>10</v>
+      <c r="B7" t="s">
+        <v>26</v>
       </c>
       <c r="C7" s="1">
-        <v>0</v>
+        <v>1026</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
       </c>
-      <c r="E7" s="1">
-        <v>0</v>
+      <c r="E7">
+        <v>5004</v>
       </c>
       <c r="F7" s="3">
         <v>1328</v>
@@ -639,7 +642,7 @@
         <v>2104</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8" s="1">
         <v>1091</v>
@@ -659,16 +662,16 @@
         <v>2105</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="1">
-        <v>0</v>
+        <v>1204</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
       </c>
-      <c r="E9" s="1">
-        <v>0</v>
+      <c r="E9">
+        <v>5005</v>
       </c>
       <c r="F9" s="3">
         <v>1328</v>
@@ -679,16 +682,16 @@
         <v>2106</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1">
-        <v>0</v>
+        <v>1205</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
-      <c r="E10" s="1">
-        <v>0</v>
+      <c r="E10">
+        <v>5006</v>
       </c>
       <c r="F10" s="3">
         <v>1328</v>
@@ -699,7 +702,7 @@
         <v>2107</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" s="1">
         <v>0</v>
@@ -711,7 +714,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -719,7 +722,7 @@
         <v>2108</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="1">
         <v>0</v>
@@ -731,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -739,7 +742,7 @@
         <v>2109</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" s="1">
         <v>0</v>
@@ -751,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -759,7 +762,7 @@
         <v>2110</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14" s="1">
         <v>0</v>
@@ -771,7 +774,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -779,7 +782,7 @@
         <v>2111</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" s="1">
         <v>1017</v>
@@ -799,7 +802,7 @@
         <v>2112</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" s="1">
         <v>0</v>
@@ -819,7 +822,7 @@
         <v>2113</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" s="1">
         <v>0</v>
@@ -836,30 +839,30 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>2200</v>
+        <v>2114</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C18" s="1">
-        <v>0</v>
+        <v>1119</v>
       </c>
       <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>5002</v>
       </c>
       <c r="F18" s="3">
-        <v>405</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C19" s="1">
         <v>0</v>
@@ -871,6 +874,26 @@
         <v>0</v>
       </c>
       <c r="F19" s="3">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>2201</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>405</v>
       </c>
     </row>

--- a/Datas/HomeEquipmentData.xlsx
+++ b/Datas/HomeEquipmentData.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -153,6 +153,14 @@
   </si>
   <si>
     <t>蒸煮锅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>柴墩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>759</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -507,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:F20"/>
+  <dimension ref="A2:F21"/>
   <sheetFormatPr defaultColWidth="9.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.75" style="1"/>
@@ -859,30 +867,30 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>2200</v>
+        <v>2115</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C19" s="1">
-        <v>0</v>
+        <v>1054</v>
       </c>
       <c r="D19" s="1">
-        <v>1</v>
-      </c>
-      <c r="E19" s="1">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3">
-        <v>405</v>
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>5010</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C20" s="1">
         <v>0</v>
@@ -894,6 +902,26 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>2201</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>405</v>
       </c>
     </row>

--- a/Datas/HomeEquipmentData.xlsx
+++ b/Datas/HomeEquipmentData.xlsx
@@ -80,10 +80,6 @@
     <t>List&lt;int&gt;</t>
   </si>
   <si>
-    <t>纺织机</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>锻造炉</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -162,6 +158,10 @@
   <si>
     <t>759</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>缝纫机</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -556,10 +556,10 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>3</v>
@@ -570,10 +570,10 @@
         <v>2100</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C4" s="1">
-        <v>1201</v>
+        <v>1207</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -590,7 +590,7 @@
         <v>2101</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="1">
         <v>1202</v>
@@ -610,7 +610,7 @@
         <v>2102</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" s="1">
         <v>1023</v>
@@ -630,7 +630,7 @@
         <v>2103</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1">
         <v>1026</v>
@@ -650,7 +650,7 @@
         <v>2104</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="1">
         <v>1091</v>
@@ -670,7 +670,7 @@
         <v>2105</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" s="1">
         <v>1204</v>
@@ -690,7 +690,7 @@
         <v>2106</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="1">
         <v>1205</v>
@@ -710,7 +710,7 @@
         <v>2107</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1">
         <v>0</v>
@@ -722,7 +722,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -730,7 +730,7 @@
         <v>2108</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" s="1">
         <v>0</v>
@@ -742,7 +742,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -750,7 +750,7 @@
         <v>2109</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13" s="1">
         <v>0</v>
@@ -762,7 +762,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -770,7 +770,7 @@
         <v>2110</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" s="1">
         <v>0</v>
@@ -782,7 +782,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -790,7 +790,7 @@
         <v>2111</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15" s="1">
         <v>1017</v>
@@ -810,7 +810,7 @@
         <v>2112</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C16" s="1">
         <v>0</v>
@@ -830,7 +830,7 @@
         <v>2113</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C17" s="1">
         <v>0</v>
@@ -850,7 +850,7 @@
         <v>2114</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="1">
         <v>1119</v>
@@ -870,7 +870,7 @@
         <v>2115</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C19" s="1">
         <v>1054</v>
@@ -882,7 +882,7 @@
         <v>5010</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -890,7 +890,7 @@
         <v>2200</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C20" s="1">
         <v>0</v>
@@ -910,7 +910,7 @@
         <v>2201</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C21" s="1">
         <v>0</v>

--- a/Datas/HomeEquipmentData.xlsx
+++ b/Datas/HomeEquipmentData.xlsx
@@ -24,7 +24,7 @@
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0" shapeId="0">
+    <comment ref="E3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -53,38 +53,137 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="66">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>mapItemDataId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>canSetMaps</t>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>List&lt;int&gt;</t>
+  </si>
+  <si>
+    <t>锻造炉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>烘烤炉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冷餐台</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>酿造桶</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>绘写台</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰箱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>储物箱(木)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>储物箱(银)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>储物箱(金)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通柜台</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器柜台</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>服饰架</t>
+  </si>
+  <si>
+    <t>沙发</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>双人床</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>homeEquipType</t>
+  </si>
+  <si>
+    <t>1328,547,405</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>manufatureId</t>
+  </si>
+  <si>
+    <t>柴墩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>759</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>info</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>equipmentName</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>mapItemDataId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>canSetMaps</t>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>List&lt;int&gt;</t>
+    <t>缝纫机</t>
+  </si>
+  <si>
+    <t>缝纫机</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蒸煮锅</t>
+  </si>
+  <si>
+    <t>蒸煮锅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>搅拌器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>锻造炉</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>烘烤炉</t>
+    <t>烤炉</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -104,19 +203,19 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>储物箱(木)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>储物箱(银)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>储物箱(金)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>普通柜台</t>
+    <t>木箱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>银箱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>金箱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>柜台</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -125,9 +224,6 @@
   </si>
   <si>
     <t>服饰架</t>
-  </si>
-  <si>
-    <t>沙发</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -135,33 +231,84 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>homeEquipType</t>
-  </si>
-  <si>
-    <t>1328,547,405</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>manufatureId</t>
+    <t>用来制作衣物的设备</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来制作武器的设备</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来烘烤食物的设备</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来制作蒸煮食物的设备</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来制作冷餐的设备</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来酿造酒水饮料的设备</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来绘写卷轴的设备</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来保存新鲜物品的设备</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>木质的储物箱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>银质的储物箱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>金质的储物箱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>通用的柜台，可放置一般商品</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>放置武器的柜台</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>放置服饰的架子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>柔软舒适的座位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来搅拌食材的设备</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提供给夫妇两人休息的床</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>搅拌器</t>
-  </si>
-  <si>
-    <t>蒸煮锅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iconName</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>柴墩</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>759</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>缝纫机</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -224,7 +371,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -234,6 +381,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -515,205 +665,262 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:F21"/>
+  <dimension ref="A2:H21"/>
   <sheetFormatPr defaultColWidth="9.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.75" style="1"/>
-    <col min="2" max="4" width="16.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15" style="1" customWidth="1"/>
-    <col min="6" max="6" width="48.125" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.75" style="1"/>
+    <col min="2" max="2" width="16.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="1" customWidth="1"/>
+    <col min="4" max="5" width="16.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H3" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2100</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="1">
+      <c r="D4" s="1">
         <v>1207</v>
       </c>
-      <c r="D4" s="1">
-        <v>0</v>
-      </c>
-      <c r="E4">
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>5007</v>
       </c>
-      <c r="F4" s="3">
+      <c r="G4" s="3">
         <v>1328</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H4" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2101</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="1">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="1">
         <v>1202</v>
       </c>
-      <c r="D5" s="1">
-        <v>0</v>
-      </c>
-      <c r="E5">
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>5008</v>
       </c>
-      <c r="F5" s="3">
+      <c r="G5" s="3">
         <v>1328</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H5" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>2102</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="1">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="1">
         <v>1023</v>
       </c>
-      <c r="D6" s="1">
-        <v>0</v>
-      </c>
-      <c r="E6">
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>5003</v>
       </c>
-      <c r="F6" s="3">
+      <c r="G6" s="3">
         <v>1328</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H6" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>2103</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="1">
+        <v>31</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="1">
         <v>1026</v>
       </c>
-      <c r="D7" s="1">
-        <v>0</v>
-      </c>
-      <c r="E7">
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>5004</v>
       </c>
-      <c r="F7" s="3">
+      <c r="G7" s="3">
         <v>1328</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H7" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2104</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="1">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="1">
         <v>1091</v>
       </c>
-      <c r="D8" s="1">
-        <v>0</v>
-      </c>
       <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
         <v>5001</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1328</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H8" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>2105</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="1">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="1">
         <v>1204</v>
       </c>
-      <c r="D9" s="1">
-        <v>0</v>
-      </c>
-      <c r="E9">
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9">
         <v>5005</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1328</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H9" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>2106</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="1">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="1">
         <v>1205</v>
       </c>
-      <c r="D10" s="1">
-        <v>0</v>
-      </c>
-      <c r="E10">
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10">
         <v>5006</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1328</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H10" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>2107</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="1">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -721,19 +928,25 @@
       <c r="E11" s="1">
         <v>0</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>2108</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="1">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -741,19 +954,25 @@
       <c r="E12" s="1">
         <v>0</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>2109</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="1">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -761,19 +980,25 @@
       <c r="E13" s="1">
         <v>0</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>2110</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="1">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -781,39 +1006,51 @@
       <c r="E14" s="1">
         <v>0</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>2111</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="1">
+        <v>15</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="1">
         <v>1017</v>
       </c>
-      <c r="D15" s="1">
-        <v>0</v>
-      </c>
       <c r="E15" s="1">
         <v>0</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
         <v>547</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H15" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>2112</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="1">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -821,19 +1058,25 @@
       <c r="E16" s="1">
         <v>0</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
         <v>547</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H16" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>2113</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="1">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
@@ -841,88 +1084,115 @@
       <c r="E17" s="1">
         <v>0</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
         <v>547</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H17" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>2114</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="1">
+        <v>32</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="1">
         <v>1119</v>
       </c>
-      <c r="D18" s="1">
-        <v>0</v>
-      </c>
-      <c r="E18">
+      <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18">
         <v>5002</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1328</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H18" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>2115</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="1">
+        <v>23</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="1">
         <v>1054</v>
       </c>
-      <c r="D19" s="1">
-        <v>0</v>
-      </c>
-      <c r="E19">
+      <c r="E19" s="1">
+        <v>0</v>
+      </c>
+      <c r="F19">
         <v>5010</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G19" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>2200</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="1">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="D20" s="1">
+        <v>0</v>
+      </c>
+      <c r="E20" s="1">
         <v>1</v>
       </c>
-      <c r="E20" s="1">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>405</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H20" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>2201</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="1">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="D21" s="1">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1">
         <v>1</v>
       </c>
-      <c r="E21" s="1">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3">
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
         <v>405</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/HomeEquipmentData.xlsx
+++ b/Datas/HomeEquipmentData.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="63">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -116,10 +116,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>武器柜台</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>服饰架</t>
   </si>
   <si>
@@ -219,10 +215,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>武器柜台</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>服饰架</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -276,10 +268,6 @@
   </si>
   <si>
     <t>通用的柜台，可放置一般商品</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>放置武器的柜台</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -665,7 +653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:H21"/>
+  <dimension ref="A2:H20"/>
   <sheetFormatPr defaultColWidth="9.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.75" style="1"/>
@@ -701,7 +689,7 @@
         <v>5</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -709,25 +697,25 @@
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -735,10 +723,10 @@
         <v>2100</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4" s="1">
         <v>1207</v>
@@ -753,7 +741,7 @@
         <v>1328</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -764,7 +752,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" s="1">
         <v>1202</v>
@@ -779,7 +767,7 @@
         <v>1328</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -790,7 +778,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D6" s="1">
         <v>1023</v>
@@ -805,7 +793,7 @@
         <v>1328</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -813,10 +801,10 @@
         <v>2103</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1">
         <v>1026</v>
@@ -831,7 +819,7 @@
         <v>1328</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -842,7 +830,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" s="1">
         <v>1091</v>
@@ -857,7 +845,7 @@
         <v>1328</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -868,7 +856,7 @@
         <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D9" s="1">
         <v>1204</v>
@@ -883,7 +871,7 @@
         <v>1328</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -894,7 +882,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D10" s="1">
         <v>1205</v>
@@ -909,7 +897,7 @@
         <v>1328</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -920,7 +908,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -932,10 +920,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -946,7 +934,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -958,10 +946,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -972,7 +960,7 @@
         <v>13</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -984,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -998,7 +986,7 @@
         <v>14</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -1010,10 +998,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -1024,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D15" s="1">
         <v>1017</v>
@@ -1039,18 +1027,18 @@
         <v>547</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -1065,93 +1053,93 @@
         <v>547</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D17" s="1">
-        <v>0</v>
+        <v>1119</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
       </c>
-      <c r="F17" s="1">
-        <v>0</v>
+      <c r="F17">
+        <v>5002</v>
       </c>
       <c r="G17" s="3">
-        <v>547</v>
+        <v>1328</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D18" s="1">
-        <v>1119</v>
+        <v>1054</v>
       </c>
       <c r="E18" s="1">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>5002</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1328</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>60</v>
+        <v>5010</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>2115</v>
+        <v>2200</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="D19" s="1">
-        <v>1054</v>
+        <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>5010</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>24</v>
+        <v>1</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3">
+        <v>405</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -1166,33 +1154,7 @@
         <v>405</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="2">
-        <v>2201</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21" s="1">
-        <v>0</v>
-      </c>
-      <c r="E21" s="1">
-        <v>1</v>
-      </c>
-      <c r="F21" s="1">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3">
-        <v>405</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/HomeEquipmentData.xlsx
+++ b/Datas/HomeEquipmentData.xlsx
@@ -48,12 +48,38 @@
         </r>
       </text>
     </comment>
+    <comment ref="F3" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>装饰=0,床=1, 箱子=2,柜台=3,生产=4</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="66">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -134,9 +160,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>manufatureId</t>
-  </si>
-  <si>
     <t>柴墩</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -297,13 +320,27 @@
   <si>
     <t>柴墩</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>homeEquipFuncValue</t>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>homeEquipFunc</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -336,6 +373,21 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -653,20 +705,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:H20"/>
+  <dimension ref="A2:I20"/>
   <sheetFormatPr defaultColWidth="9.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.75" style="1"/>
     <col min="2" max="2" width="16.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="1" customWidth="1"/>
-    <col min="4" max="5" width="16.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.75" style="1"/>
+    <col min="4" max="7" width="16.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.875" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -683,24 +734,27 @@
         <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>1</v>
@@ -709,24 +763,27 @@
         <v>19</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I3" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2100</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" s="1">
         <v>1207</v>
@@ -734,17 +791,20 @@
       <c r="E4" s="1">
         <v>0</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
+        <v>4</v>
+      </c>
+      <c r="G4">
         <v>5007</v>
       </c>
-      <c r="G4" s="3">
+      <c r="H4" s="3">
         <v>1328</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I4" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2101</v>
       </c>
@@ -752,7 +812,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" s="1">
         <v>1202</v>
@@ -760,17 +820,20 @@
       <c r="E5" s="1">
         <v>0</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
+        <v>4</v>
+      </c>
+      <c r="G5">
         <v>5008</v>
       </c>
-      <c r="G5" s="3">
+      <c r="H5" s="3">
         <v>1328</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I5" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>2102</v>
       </c>
@@ -778,7 +841,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" s="1">
         <v>1023</v>
@@ -786,25 +849,28 @@
       <c r="E6" s="1">
         <v>0</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
+        <v>4</v>
+      </c>
+      <c r="G6">
         <v>5003</v>
       </c>
-      <c r="G6" s="3">
+      <c r="H6" s="3">
         <v>1328</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I6" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>2103</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D7" s="1">
         <v>1026</v>
@@ -812,17 +878,20 @@
       <c r="E7" s="1">
         <v>0</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
+        <v>4</v>
+      </c>
+      <c r="G7">
         <v>5004</v>
       </c>
-      <c r="G7" s="3">
+      <c r="H7" s="3">
         <v>1328</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I7" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2104</v>
       </c>
@@ -830,7 +899,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" s="1">
         <v>1091</v>
@@ -839,16 +908,19 @@
         <v>0</v>
       </c>
       <c r="F8" s="1">
+        <v>4</v>
+      </c>
+      <c r="G8" s="1">
         <v>5001</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1328</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I8" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>2105</v>
       </c>
@@ -856,7 +928,7 @@
         <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D9" s="1">
         <v>1204</v>
@@ -864,17 +936,20 @@
       <c r="E9" s="1">
         <v>0</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
+        <v>4</v>
+      </c>
+      <c r="G9">
         <v>5005</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1328</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I9" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>2106</v>
       </c>
@@ -882,7 +957,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D10" s="1">
         <v>1205</v>
@@ -890,17 +965,20 @@
       <c r="E10" s="1">
         <v>0</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
+        <v>4</v>
+      </c>
+      <c r="G10">
         <v>5006</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1328</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I10" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>2107</v>
       </c>
@@ -908,7 +986,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -917,16 +995,19 @@
         <v>0</v>
       </c>
       <c r="F11" s="1">
-        <v>0</v>
-      </c>
-      <c r="G11" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="1">
+        <v>2</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I11" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>2108</v>
       </c>
@@ -934,7 +1015,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -943,16 +1024,19 @@
         <v>0</v>
       </c>
       <c r="F12" s="1">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G12" s="1">
+        <v>3</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I12" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>2109</v>
       </c>
@@ -960,7 +1044,7 @@
         <v>13</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -969,16 +1053,19 @@
         <v>0</v>
       </c>
       <c r="F13" s="1">
-        <v>0</v>
-      </c>
-      <c r="G13" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G13" s="1">
+        <v>3</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I13" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>2110</v>
       </c>
@@ -986,7 +1073,7 @@
         <v>14</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -995,16 +1082,19 @@
         <v>0</v>
       </c>
       <c r="F14" s="1">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" s="1">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I14" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>2111</v>
       </c>
@@ -1012,7 +1102,7 @@
         <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D15" s="1">
         <v>1017</v>
@@ -1021,16 +1111,19 @@
         <v>0</v>
       </c>
       <c r="F15" s="1">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
+        <v>3</v>
+      </c>
+      <c r="G15" s="1">
+        <v>300</v>
+      </c>
+      <c r="H15" s="3">
         <v>547</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I15" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>2113</v>
       </c>
@@ -1038,7 +1131,7 @@
         <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -1047,24 +1140,27 @@
         <v>0</v>
       </c>
       <c r="F16" s="1">
-        <v>0</v>
-      </c>
-      <c r="G16" s="3">
+        <v>3</v>
+      </c>
+      <c r="G16" s="1">
+        <v>301</v>
+      </c>
+      <c r="H16" s="3">
         <v>547</v>
       </c>
-      <c r="H16" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I16" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>2114</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D17" s="1">
         <v>1119</v>
@@ -1072,25 +1168,28 @@
       <c r="E17" s="1">
         <v>0</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
+        <v>4</v>
+      </c>
+      <c r="G17">
         <v>5002</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1328</v>
       </c>
-      <c r="H17" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I17" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>2115</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D18" s="1">
         <v>1054</v>
@@ -1098,14 +1197,17 @@
       <c r="E18" s="1">
         <v>0</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
+        <v>4</v>
+      </c>
+      <c r="G18">
         <v>5010</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H18" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>2200</v>
       </c>
@@ -1124,14 +1226,17 @@
       <c r="F19" s="1">
         <v>0</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3">
         <v>405</v>
       </c>
-      <c r="H19" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I19" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>2201</v>
       </c>
@@ -1139,7 +1244,7 @@
         <v>18</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -1148,13 +1253,16 @@
         <v>1</v>
       </c>
       <c r="F20" s="1">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>405</v>
       </c>
-      <c r="H20" s="4" t="s">
-        <v>59</v>
+      <c r="I20" s="4" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/HomeEquipmentData.xlsx
+++ b/Datas/HomeEquipmentData.xlsx
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="68">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -334,6 +334,14 @@
   </si>
   <si>
     <t>homeEquipFunc</t>
+  </si>
+  <si>
+    <t>武器架</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>放置武器的架子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -705,7 +713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:I20"/>
+  <dimension ref="A2:I21"/>
   <sheetFormatPr defaultColWidth="9.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.75" style="1"/>
@@ -1134,7 +1142,7 @@
         <v>41</v>
       </c>
       <c r="D16" s="1">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="E16" s="1">
         <v>0</v>
@@ -1209,42 +1217,42 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>2200</v>
+        <v>2116</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="D19" s="1">
-        <v>0</v>
+        <v>1022</v>
       </c>
       <c r="E19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="H19" s="3">
-        <v>405</v>
+        <v>547</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -1253,7 +1261,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
@@ -1262,6 +1270,35 @@
         <v>405</v>
       </c>
       <c r="I20" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>2201</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>405</v>
+      </c>
+      <c r="I21" s="4" t="s">
         <v>58</v>
       </c>
     </row>

--- a/Datas/HomeEquipmentData.xlsx
+++ b/Datas/HomeEquipmentData.xlsx
@@ -126,6 +126,212 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>普通柜台</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>服饰架</t>
+  </si>
+  <si>
+    <t>沙发</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>双人床</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>homeEquipType</t>
+  </si>
+  <si>
+    <t>1328,547,405</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>柴墩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>759</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>info</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>equipmentName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>缝纫机</t>
+  </si>
+  <si>
+    <t>缝纫机</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蒸煮锅</t>
+  </si>
+  <si>
+    <t>蒸煮锅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>搅拌器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>锻造炉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤炉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冷餐台</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>酿造桶</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>绘写台</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰箱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>木箱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>银箱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>金箱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>柜台</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>服饰架</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>双人床</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来制作衣物的设备</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来制作武器的设备</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来烘烤食物的设备</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来制作蒸煮食物的设备</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来制作冷餐的设备</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来酿造酒水饮料的设备</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来绘写卷轴的设备</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来保存新鲜物品的设备</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>木质的储物箱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>银质的储物箱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>金质的储物箱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>通用的柜台，可放置一般商品</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>放置服饰的架子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>柔软舒适的座位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用来搅拌食材的设备</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提供给夫妇两人休息的床</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>搅拌器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iconName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>柴墩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>homeEquipFuncValue</t>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>homeEquipFunc</t>
+  </si>
+  <si>
+    <t>武器架</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>放置武器的架子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>储物箱(木)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -135,212 +341,6 @@
   </si>
   <si>
     <t>储物箱(金)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>普通柜台</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>服饰架</t>
-  </si>
-  <si>
-    <t>沙发</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>双人床</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>homeEquipType</t>
-  </si>
-  <si>
-    <t>1328,547,405</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>柴墩</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>759</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>info</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>equipmentName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>缝纫机</t>
-  </si>
-  <si>
-    <t>缝纫机</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>蒸煮锅</t>
-  </si>
-  <si>
-    <t>蒸煮锅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>搅拌器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>锻造炉</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>烤炉</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>冷餐台</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>酿造桶</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>绘写台</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰箱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>木箱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>银箱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>金箱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>柜台</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>服饰架</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>双人床</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>用来制作衣物的设备</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>用来制作武器的设备</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>用来烘烤食物的设备</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>用来制作蒸煮食物的设备</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>用来制作冷餐的设备</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>用来酿造酒水饮料的设备</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>用来绘写卷轴的设备</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>用来保存新鲜物品的设备</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>木质的储物箱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>银质的储物箱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>金质的储物箱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>通用的柜台，可放置一般商品</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>放置服饰的架子</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>柔软舒适的座位</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>用来搅拌食材的设备</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>提供给夫妇两人休息的床</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>搅拌器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>iconName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>柴墩</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>homeEquipFuncValue</t>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>homeEquipFunc</t>
-  </si>
-  <si>
-    <t>武器架</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>放置武器的架子</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -742,16 +742,16 @@
         <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -759,28 +759,28 @@
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -788,10 +788,10 @@
         <v>2100</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D4" s="1">
         <v>1207</v>
@@ -809,7 +809,7 @@
         <v>1328</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -820,7 +820,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D5" s="1">
         <v>1202</v>
@@ -838,7 +838,7 @@
         <v>1328</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -849,7 +849,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1">
         <v>1023</v>
@@ -867,7 +867,7 @@
         <v>1328</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -875,10 +875,10 @@
         <v>2103</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D7" s="1">
         <v>1026</v>
@@ -896,7 +896,7 @@
         <v>1328</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -907,7 +907,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D8" s="1">
         <v>1091</v>
@@ -925,7 +925,7 @@
         <v>1328</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -936,7 +936,7 @@
         <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D9" s="1">
         <v>1204</v>
@@ -954,7 +954,7 @@
         <v>1328</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
@@ -965,7 +965,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D10" s="1">
         <v>1205</v>
@@ -983,7 +983,7 @@
         <v>1328</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
@@ -994,7 +994,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -1009,10 +1009,10 @@
         <v>2</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
@@ -1020,10 +1020,10 @@
         <v>2108</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -1035,13 +1035,13 @@
         <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
@@ -1049,10 +1049,10 @@
         <v>2109</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -1064,13 +1064,13 @@
         <v>2</v>
       </c>
       <c r="G13" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
@@ -1078,10 +1078,10 @@
         <v>2110</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -1093,13 +1093,13 @@
         <v>2</v>
       </c>
       <c r="G14" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
@@ -1107,10 +1107,10 @@
         <v>2111</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D15" s="1">
         <v>1017</v>
@@ -1128,7 +1128,7 @@
         <v>547</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
@@ -1136,10 +1136,10 @@
         <v>2113</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D16" s="1">
         <v>1023</v>
@@ -1157,7 +1157,7 @@
         <v>547</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
@@ -1165,10 +1165,10 @@
         <v>2114</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D17" s="1">
         <v>1119</v>
@@ -1186,7 +1186,7 @@
         <v>1328</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
@@ -1194,10 +1194,10 @@
         <v>2115</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D18" s="1">
         <v>1054</v>
@@ -1212,7 +1212,7 @@
         <v>5010</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
@@ -1220,10 +1220,10 @@
         <v>2116</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D19" s="1">
         <v>1022</v>
@@ -1241,7 +1241,7 @@
         <v>547</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
@@ -1249,10 +1249,10 @@
         <v>2200</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -1270,7 +1270,7 @@
         <v>405</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
@@ -1278,10 +1278,10 @@
         <v>2201</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
@@ -1299,7 +1299,7 @@
         <v>405</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/HomeEquipmentData.xlsx
+++ b/Datas/HomeEquipmentData.xlsx
@@ -997,7 +997,7 @@
         <v>33</v>
       </c>
       <c r="D11" s="1">
-        <v>0</v>
+        <v>1120</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>34</v>
       </c>
       <c r="D12" s="1">
-        <v>0</v>
+        <v>1121</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
@@ -1055,7 +1055,7 @@
         <v>35</v>
       </c>
       <c r="D13" s="1">
-        <v>0</v>
+        <v>1122</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
@@ -1084,7 +1084,7 @@
         <v>36</v>
       </c>
       <c r="D14" s="1">
-        <v>0</v>
+        <v>1123</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>

--- a/Datas/HomeEquipmentData.xlsx
+++ b/Datas/HomeEquipmentData.xlsx
@@ -32,6 +32,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve"> 生产设施,生活设施</t>
@@ -41,6 +42,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -79,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="100">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -133,10 +135,6 @@
     <t>服饰架</t>
   </si>
   <si>
-    <t>沙发</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>双人床</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -290,10 +288,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>用来搅拌食材的设备</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>提供给夫妇两人休息的床</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -342,13 +336,142 @@
   <si>
     <t>储物箱(金)</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>壁炉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绿意盎然的装饰品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以养殖捕获的鱼类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在寒冷的季节里感受温暖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>盆栽1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>盆栽2</t>
+  </si>
+  <si>
+    <t>盆栽3</t>
+  </si>
+  <si>
+    <t>盆栽4</t>
+  </si>
+  <si>
+    <t>盆栽5</t>
+  </si>
+  <si>
+    <t>盆栽6</t>
+  </si>
+  <si>
+    <t>砖墙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>木饰墙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大理石墙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石砖墙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>青砖墙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>原木墙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>木板墙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>木板墙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>木制的墙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用原木制作的墙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用红砖制作的墙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>经过装饰过的木墙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大理石制作的墙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石砖制作的墙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用青砖制作的墙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>圆鱼缸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>方鱼缸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙发(红)</t>
+  </si>
+  <si>
+    <t>沙发(红)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙发(蓝)</t>
+  </si>
+  <si>
+    <t>柔软的双人沙发</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>绿意盎然的装饰品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hide</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -369,19 +492,6 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -713,19 +823,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:I21"/>
+  <dimension ref="A2:J38"/>
   <sheetFormatPr defaultColWidth="9.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.75" style="1"/>
     <col min="2" max="2" width="16.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="1" customWidth="1"/>
-    <col min="4" max="7" width="16.875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.875" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.75" style="1"/>
+    <col min="4" max="8" width="16.875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -742,56 +852,62 @@
         <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2100</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1">
         <v>1207</v>
@@ -802,17 +918,20 @@
       <c r="F4" s="1">
         <v>4</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4">
         <v>5007</v>
       </c>
-      <c r="H4" s="3">
+      <c r="I4" s="3">
         <v>1328</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J4" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2101</v>
       </c>
@@ -820,7 +939,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" s="1">
         <v>1202</v>
@@ -831,17 +950,20 @@
       <c r="F5" s="1">
         <v>4</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>5008</v>
       </c>
-      <c r="H5" s="3">
+      <c r="I5" s="3">
         <v>1328</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J5" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>2102</v>
       </c>
@@ -849,7 +971,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" s="1">
         <v>1023</v>
@@ -860,25 +982,28 @@
       <c r="F6" s="1">
         <v>4</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>5003</v>
       </c>
-      <c r="H6" s="3">
+      <c r="I6" s="3">
         <v>1328</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J6" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>2103</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" s="1">
         <v>1026</v>
@@ -889,17 +1014,20 @@
       <c r="F7" s="1">
         <v>4</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>5004</v>
       </c>
-      <c r="H7" s="3">
+      <c r="I7" s="3">
         <v>1328</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J7" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2104</v>
       </c>
@@ -907,7 +1035,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" s="1">
         <v>1091</v>
@@ -918,17 +1046,20 @@
       <c r="F8" s="1">
         <v>4</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
         <v>5001</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1328</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J8" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>2105</v>
       </c>
@@ -936,7 +1067,7 @@
         <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D9" s="1">
         <v>1204</v>
@@ -947,17 +1078,20 @@
       <c r="F9" s="1">
         <v>4</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9">
         <v>5005</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1328</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J9" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>2106</v>
       </c>
@@ -965,7 +1099,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D10" s="1">
         <v>1205</v>
@@ -976,17 +1110,20 @@
       <c r="F10" s="1">
         <v>4</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10">
         <v>5006</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1328</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J10" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>2107</v>
       </c>
@@ -994,7 +1131,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D11" s="1">
         <v>1120</v>
@@ -1005,25 +1142,28 @@
       <c r="F11" s="1">
         <v>2</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
         <v>2</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>2108</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D12" s="1">
         <v>1121</v>
@@ -1034,25 +1174,28 @@
       <c r="F12" s="1">
         <v>2</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
         <v>5</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>2109</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D13" s="1">
         <v>1122</v>
@@ -1063,25 +1206,28 @@
       <c r="F13" s="1">
         <v>2</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
         <v>6</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>2110</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" s="1">
         <v>1123</v>
@@ -1092,17 +1238,20 @@
       <c r="F14" s="1">
         <v>2</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
         <v>7</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>2111</v>
       </c>
@@ -1110,7 +1259,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" s="1">
         <v>1017</v>
@@ -1121,17 +1270,20 @@
       <c r="F15" s="1">
         <v>3</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
         <v>300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>547</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J15" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>2113</v>
       </c>
@@ -1139,7 +1291,7 @@
         <v>13</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D16" s="1">
         <v>1023</v>
@@ -1150,25 +1302,28 @@
       <c r="F16" s="1">
         <v>3</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
         <v>301</v>
       </c>
-      <c r="H16" s="3">
+      <c r="I16" s="3">
         <v>547</v>
       </c>
-      <c r="I16" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J16" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>2114</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D17" s="1">
         <v>1119</v>
@@ -1179,25 +1334,28 @@
       <c r="F17" s="1">
         <v>4</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <v>5002</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1328</v>
       </c>
-      <c r="I17" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J17" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>2115</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D18" s="1">
         <v>1054</v>
@@ -1208,22 +1366,25 @@
       <c r="F18" s="1">
         <v>4</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18">
         <v>5010</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I18" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>2116</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D19" s="1">
         <v>1022</v>
@@ -1234,17 +1395,20 @@
       <c r="F19" s="1">
         <v>3</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
         <v>302</v>
       </c>
-      <c r="H19" s="3">
+      <c r="I19" s="3">
         <v>547</v>
       </c>
-      <c r="I19" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J19" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>2200</v>
       </c>
@@ -1252,60 +1416,610 @@
         <v>14</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D20" s="1">
-        <v>0</v>
+        <v>1170</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
       </c>
       <c r="F20" s="1">
-        <v>0</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>405</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>2201</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="D21" s="1">
-        <v>0</v>
+        <v>1172</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
       </c>
       <c r="F21" s="1">
-        <v>1</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3">
-        <v>405</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>55</v>
+        <v>0</v>
+      </c>
+      <c r="G21" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>2202</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1171</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
+        <v>2203</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1173</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <v>2204</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1174</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="2">
+        <v>2205</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1175</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="2">
+        <v>2206</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1176</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" s="2">
+        <v>2207</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1177</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" s="2">
+        <v>2208</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1178</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A29" s="2">
+        <v>2209</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1069</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+      <c r="F29" s="1">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A30" s="2">
+        <v>2210</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1179</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1</v>
+      </c>
+      <c r="F30" s="1">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A31" s="2">
+        <v>2211</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1180</v>
+      </c>
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
+        <v>2212</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0</v>
+      </c>
+      <c r="E32" s="1">
+        <v>1</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" s="2">
+        <v>2213</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D33" s="1">
+        <v>0</v>
+      </c>
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A34" s="2">
+        <v>2214</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0</v>
+      </c>
+      <c r="E34" s="1">
+        <v>1</v>
+      </c>
+      <c r="F34" s="1">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35" s="2">
+        <v>2215</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" s="1">
+        <v>0</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36" s="2">
+        <v>2216</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D36" s="1">
+        <v>0</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1">
+        <v>0</v>
+      </c>
+      <c r="G36" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A37" s="2">
+        <v>2217</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37" s="1">
+        <v>0</v>
+      </c>
+      <c r="E37" s="1">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" s="2">
+        <v>2218</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D38" s="1">
+        <v>0</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Datas/HomeEquipmentData.xlsx
+++ b/Datas/HomeEquipmentData.xlsx
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="99">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -173,13 +173,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>蒸煮锅</t>
-  </si>
-  <si>
-    <t>蒸煮锅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>搅拌器</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -464,6 +457,10 @@
   </si>
   <si>
     <t>hide</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炖煮锅</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -852,13 +849,13 @@
         <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>5</v>
@@ -875,7 +872,7 @@
         <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>1</v>
@@ -884,13 +881,13 @@
         <v>15</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>2</v>
@@ -928,7 +925,7 @@
         <v>1328</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -939,7 +936,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D5" s="1">
         <v>1202</v>
@@ -960,7 +957,7 @@
         <v>1328</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -971,10 +968,10 @@
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D6" s="1">
-        <v>1023</v>
+        <v>1203</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
@@ -992,7 +989,7 @@
         <v>1328</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -1000,13 +997,13 @@
         <v>2103</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
+      </c>
+      <c r="C7" t="s">
+        <v>98</v>
       </c>
       <c r="D7" s="1">
-        <v>1026</v>
+        <v>1206</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
@@ -1024,7 +1021,7 @@
         <v>1328</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -1035,7 +1032,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D8" s="1">
         <v>1091</v>
@@ -1056,7 +1053,7 @@
         <v>1328</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -1067,7 +1064,7 @@
         <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D9" s="1">
         <v>1204</v>
@@ -1088,7 +1085,7 @@
         <v>1328</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -1099,7 +1096,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D10" s="1">
         <v>1205</v>
@@ -1120,7 +1117,7 @@
         <v>1328</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -1131,7 +1128,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1">
         <v>1120</v>
@@ -1152,7 +1149,7 @@
         <v>16</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -1160,10 +1157,10 @@
         <v>2108</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D12" s="1">
         <v>1121</v>
@@ -1184,7 +1181,7 @@
         <v>16</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -1192,10 +1189,10 @@
         <v>2109</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D13" s="1">
         <v>1122</v>
@@ -1216,7 +1213,7 @@
         <v>16</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -1224,10 +1221,10 @@
         <v>2110</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D14" s="1">
         <v>1123</v>
@@ -1248,7 +1245,7 @@
         <v>16</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -1259,7 +1256,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D15" s="1">
         <v>1017</v>
@@ -1280,7 +1277,7 @@
         <v>547</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -1291,7 +1288,7 @@
         <v>13</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D16" s="1">
         <v>1023</v>
@@ -1312,7 +1309,7 @@
         <v>547</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
@@ -1320,10 +1317,10 @@
         <v>2114</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D17" s="1">
         <v>1119</v>
@@ -1344,7 +1341,7 @@
         <v>1328</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
@@ -1355,7 +1352,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D18" s="1">
         <v>1054</v>
@@ -1381,10 +1378,10 @@
         <v>2116</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D19" s="1">
         <v>1022</v>
@@ -1405,7 +1402,7 @@
         <v>547</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
@@ -1416,7 +1413,7 @@
         <v>14</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D20" s="1">
         <v>1170</v>
@@ -1437,7 +1434,7 @@
         <v>16</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
@@ -1445,10 +1442,10 @@
         <v>2201</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D21" s="1">
         <v>1172</v>
@@ -1469,7 +1466,7 @@
         <v>16</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
@@ -1477,10 +1474,10 @@
         <v>2202</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D22" s="1">
         <v>1171</v>
@@ -1501,7 +1498,7 @@
         <v>16</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
@@ -1509,10 +1506,10 @@
         <v>2203</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D23" s="1">
         <v>1173</v>
@@ -1533,7 +1530,7 @@
         <v>16</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
@@ -1541,10 +1538,10 @@
         <v>2204</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D24" s="1">
         <v>1174</v>
@@ -1565,7 +1562,7 @@
         <v>16</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
@@ -1573,10 +1570,10 @@
         <v>2205</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D25" s="1">
         <v>1175</v>
@@ -1597,7 +1594,7 @@
         <v>16</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
@@ -1605,10 +1602,10 @@
         <v>2206</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D26" s="1">
         <v>1176</v>
@@ -1629,7 +1626,7 @@
         <v>16</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
@@ -1637,10 +1634,10 @@
         <v>2207</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D27" s="1">
         <v>1177</v>
@@ -1661,7 +1658,7 @@
         <v>16</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
@@ -1669,10 +1666,10 @@
         <v>2208</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D28" s="1">
         <v>1178</v>
@@ -1693,7 +1690,7 @@
         <v>16</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
@@ -1701,10 +1698,10 @@
         <v>2209</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D29" s="1">
         <v>1069</v>
@@ -1725,7 +1722,7 @@
         <v>16</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
@@ -1733,10 +1730,10 @@
         <v>2210</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D30" s="1">
         <v>1179</v>
@@ -1757,7 +1754,7 @@
         <v>16</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
@@ -1765,10 +1762,10 @@
         <v>2211</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D31" s="1">
         <v>1180</v>
@@ -1789,7 +1786,7 @@
         <v>16</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
@@ -1797,31 +1794,31 @@
         <v>2212</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0</v>
+      </c>
+      <c r="E32" s="1">
+        <v>1</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="D32" s="1">
-        <v>0</v>
-      </c>
-      <c r="E32" s="1">
-        <v>1</v>
-      </c>
-      <c r="F32" s="1">
-        <v>0</v>
-      </c>
-      <c r="G32" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="H32" s="1">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
@@ -1829,10 +1826,10 @@
         <v>2213</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
@@ -1853,7 +1850,7 @@
         <v>16</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
@@ -1861,10 +1858,10 @@
         <v>2214</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
@@ -1885,7 +1882,7 @@
         <v>16</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
@@ -1893,10 +1890,10 @@
         <v>2215</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
@@ -1917,7 +1914,7 @@
         <v>16</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
@@ -1925,10 +1922,10 @@
         <v>2216</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
@@ -1949,7 +1946,7 @@
         <v>16</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
@@ -1957,10 +1954,10 @@
         <v>2217</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
@@ -1981,7 +1978,7 @@
         <v>16</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
@@ -1989,10 +1986,10 @@
         <v>2218</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
@@ -2013,7 +2010,7 @@
         <v>16</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/HomeEquipmentData.xlsx
+++ b/Datas/HomeEquipmentData.xlsx
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="102">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -462,6 +462,16 @@
   <si>
     <t>炖煮锅</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>磨台</t>
+  </si>
+  <si>
+    <t>磨台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2527</t>
   </si>
 </sst>
 </file>
@@ -820,7 +830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:J38"/>
+  <dimension ref="A2:J39"/>
   <sheetFormatPr defaultColWidth="9.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.75" style="1"/>
@@ -1407,54 +1417,52 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>2200</v>
+        <v>2117</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="D20" s="1">
-        <v>1170</v>
+        <v>1183</v>
       </c>
       <c r="E20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G20" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <v>5009</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>51</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="J20" s="4"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>92</v>
+        <v>14</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="D21" s="1">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
       </c>
       <c r="F21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="1" t="b">
         <v>0</v>
@@ -1466,21 +1474,21 @@
         <v>16</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D22" s="1">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -1503,16 +1511,16 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>2203</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>68</v>
+        <v>2202</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="D23" s="1">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -1529,22 +1537,22 @@
       <c r="I23" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J23" s="1" t="s">
-        <v>95</v>
+      <c r="J23" s="4" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D24" s="1">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -1562,21 +1570,21 @@
         <v>16</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D25" s="1">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -1599,16 +1607,16 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D26" s="1">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -1631,16 +1639,16 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D27" s="1">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -1663,16 +1671,16 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D28" s="1">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -1693,18 +1701,18 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D29" s="1">
-        <v>1069</v>
+        <v>1178</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -1722,21 +1730,21 @@
         <v>16</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="D30" s="1">
-        <v>1179</v>
+        <v>1069</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -1754,21 +1762,21 @@
         <v>16</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D31" s="1">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -1789,18 +1797,18 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D32" s="1">
-        <v>0</v>
+        <v>1180</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -1818,18 +1826,18 @@
         <v>16</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
@@ -1850,18 +1858,18 @@
         <v>16</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
@@ -1882,18 +1890,18 @@
         <v>16</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
@@ -1914,18 +1922,18 @@
         <v>16</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
@@ -1946,18 +1954,18 @@
         <v>16</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
@@ -1978,38 +1986,70 @@
         <v>16</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
+        <v>2217</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D38" s="1">
+        <v>0</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39" s="2">
         <v>2218</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B39" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D38" s="1">
-        <v>0</v>
-      </c>
-      <c r="E38" s="1">
-        <v>1</v>
-      </c>
-      <c r="F38" s="1">
-        <v>0</v>
-      </c>
-      <c r="G38" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38" s="1">
-        <v>0</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J38" s="1" t="s">
+      <c r="D39" s="1">
+        <v>0</v>
+      </c>
+      <c r="E39" s="1">
+        <v>1</v>
+      </c>
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J39" s="1" t="s">
         <v>88</v>
       </c>
     </row>

--- a/Datas/HomeEquipmentData.xlsx
+++ b/Datas/HomeEquipmentData.xlsx
@@ -1281,7 +1281,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="I15" s="3">
         <v>547</v>
@@ -1313,7 +1313,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>301</v>
+        <v>2</v>
       </c>
       <c r="I16" s="3">
         <v>547</v>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>302</v>
+        <v>3</v>
       </c>
       <c r="I19" s="3">
         <v>547</v>
